--- a/China NEA/review_workbooks/2026-02-21_2025年光伏发电建设情况---国家能源局_review.xlsx
+++ b/China NEA/review_workbooks/2026-02-21_2025年光伏发电建设情况---国家能源局_review.xlsx
@@ -19,9 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -34,27 +32,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -75,19 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,1748 +428,999 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
       <c r="B1" t="n">
-        <v>0</v>
+        <v>31657.4</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>16357</v>
       </c>
       <c r="D1" t="n">
-        <v>2</v>
+        <v>15300.3</v>
       </c>
       <c r="E1" t="n">
-        <v>3</v>
+        <v>4594.7</v>
       </c>
       <c r="F1" t="n">
-        <v>4</v>
+        <v>119991.4</v>
       </c>
       <c r="G1" t="n">
-        <v>5</v>
+        <v>66691.39999999999</v>
       </c>
       <c r="H1" t="n">
+        <v>53300</v>
+      </c>
+      <c r="I1" t="n">
+        <v>20583.2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>202.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>303.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1027.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>474</v>
+      </c>
+      <c r="H3" t="n">
+        <v>553.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1338.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>657.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8462.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4873.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3589.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>935.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>538.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4950.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3436.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1514.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>776.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1244.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1054.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>190.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6055.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5563.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>491.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>67</v>
+      </c>
+      <c r="D7" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1554.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>609.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>945.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>683.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>61</v>
+      </c>
+      <c r="F8" t="n">
+        <v>724.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>438.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>286.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>168.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>917.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>537.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>154.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>625.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>62</v>
+      </c>
+      <c r="H10" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2803.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>972.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1831.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>513.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8968.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2567.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6401.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1701.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>311.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1390.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6429.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1145.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5284.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>612.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1314.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1096.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5625.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1659.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3965.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1812.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>476.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>415.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1734.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1597.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>616.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2872.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1400.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1472.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>784.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1871.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>823.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1048.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9484.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3416</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6068.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2940.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1216.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1169.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>591.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5565.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>677.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4888.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2897.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>974.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>894.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4484.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2228.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2256.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>496.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>901</v>
+      </c>
+      <c r="C19" t="n">
+        <v>258</v>
+      </c>
+      <c r="D19" t="n">
+        <v>643</v>
+      </c>
+      <c r="E19" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2743.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>713.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2030.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1200.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2132.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>508.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1623.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>471.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6248</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1608.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4639.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>850.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1145</v>
+      </c>
+      <c r="C21" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>672.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3273.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1391.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1882.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>69.09999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>127</v>
+      </c>
+      <c r="D22" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>960.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>598.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>275.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>585</v>
+      </c>
+      <c r="G23" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>430.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>897.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1980.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1321.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>658.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>175.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>886.3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>697.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2871.9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2573.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>298</v>
+      </c>
+      <c r="I25" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1762.9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1531.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5486.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4964.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>363.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>574.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>568.5</v>
+      </c>
+      <c r="H27" t="n">
         <v>6</v>
       </c>
-      <c r="I1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J1" t="n">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>759.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>466.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4193</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2817.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1375.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>640.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>714.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>613.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3853</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3568.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>284.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>615.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>604.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4257.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4209.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1556.9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1467.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4180.9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3916.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3415.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3402.1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9090.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9050.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I32" t="n">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省(区、市)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025年新增并网容量</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025年新增并网容量</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025年新增并网容量</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>省(区、市)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>其中：
-集中式</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>其中：
-集中式</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>省(区、市)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>其中：
-集中式</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>其中：</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>其中：
-集中式</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>光伏电</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>户用光</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>光伏电</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>其中：户</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>站</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>伏</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>站</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>用光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>31657.4</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>16357.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15300.3</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4594.7</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>119991.4</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>66691.4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>53300.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>20583.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>210.2</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>202.1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>303.7</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>122.8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>180.9</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1027.9</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>474.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>553.8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>75.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1338.8</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>657.9</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>680.9</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>284.4</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8462.9</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4873.2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3589.7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2336.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1473.3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>935.1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>538.2</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>196.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4950.5</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3436.4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1514.1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>776.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1244.6</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1054.4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>190.2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6055.5</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5563.9</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>491.6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>340.7</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>273.7</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>141.2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1554.6</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>609.1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>945.6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>683.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>56.3</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>724.5</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>438.3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>286.2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>168.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>200.1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>132.6</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>917.1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>537.8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>379.3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>154.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>213.7</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>191.5</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>625.1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>563.2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2803.9</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>972.3</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1831.6</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>513.9</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8968.4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2567.1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6401.3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2228.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1701.9</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>311.4</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1390.5</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>160.7</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6429.4</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1145.3</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5284.1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>612.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1314.2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>217.7</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1096.5</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>313.9</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>5625.5</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1659.6</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3965.8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1812.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>476.7</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>415.4</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>107.1</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1734.4</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>137.2</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1597.2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>616.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>303.4</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>281.5</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>109.9</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2872.3</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1400.2</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1472.1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>784.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1871.4</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>823.1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1048.3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>179.8</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>9484.9</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>3416.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6068.9</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2940.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1216.7</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1169.2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>591.5</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>5565.8</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>677.5</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4888.3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2897.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>974.6</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>80.4</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>894.2</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>177.3</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>4484.5</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2228.2</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2256.3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>496.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>901</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>258.0</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>643.0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>299.6</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2743.9</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>713.5</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2030.4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>1200.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2132.5</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>508.8</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1623.7</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>471.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6248.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1608.9</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4639.1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>850.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1145</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>472.5</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>672.5</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>3273.8</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1391.2</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1882.6</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>219.3</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>960.1</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>598.3</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>361.7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>275.3</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>223.9</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>585.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>154.9</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>430.1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>897.8</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>432.6</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>465.1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>151.2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1980.1</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1321.9</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>658.2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>175.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>886.3</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>697.7</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>188.5</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>130.7</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2871.9</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2573.9</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1762.9</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1531.4</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>231.5</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>155.1</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>5486.1</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>4964.6</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>521.4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>363.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>376.5</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>375.9</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>574.5</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>568.5</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>759.9</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>293.2</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>466.7</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>207.2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>4193.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2817.3</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1375.8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>640.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>714.2</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>613.8</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>3853.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3568.7</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>284.3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>615.5</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>604.9</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>4257.6</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>4209.2</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1556.9</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1467.2</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>89.7</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>4180.9</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3916.4</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>264.5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3415.4</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>3402.1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>9090.1</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>9050.1</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2210,36 +1436,29 @@
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>col_position</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ocr_header_flat</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>expected_cn</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>expected_en</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>friendly_en</t>
         </is>
@@ -2249,11 +1468,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省(区、市)</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>省(区、市)</t>
@@ -2274,6 +1489,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>2025年新增并网容量</t>
@@ -2294,11 +1510,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025年新增并网容量其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2025年新增并网容量_其中：集中式光伏电站</t>
@@ -2319,11 +1531,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025年新增并网容量其中：分布式光伏</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2025年新增并网容量_其中：分布式光伏</t>
@@ -2344,11 +1552,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025年新增并网容量其中：分布式光伏其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2025年新增并网容量_其中：户用光伏</t>
@@ -2369,11 +1573,7 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>截至2025年底累计并网容量</t>
@@ -2394,11 +1594,7 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>截至2025年底累计并网容量_其中：集中式光伏电站</t>
@@ -2419,11 +1615,7 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量其中：分布式光伏</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>截至2025年底累计并网容量_其中：分布式光伏</t>
@@ -2444,11 +1636,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>截至2025年底累计并网容量其中：分布式光伏其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>截至2025年底累计并网容量_其中：户用光伏</t>
@@ -2478,72 +1666,59 @@
   </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="31" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>province_cn</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>province_en</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_total_10kw</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_utility_10kw</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_distributed_10kw</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_residential_10kw</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_total_10kw</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_utility_10kw</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_distributed_10kw</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_residential_10kw</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>province_translation_missing</t>
         </is>
@@ -2560,28 +1735,28 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" t="n">
         <v>31657.4</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" t="n">
         <v>16357</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" t="n">
         <v>15300.3</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" t="n">
         <v>4594.7</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" t="n">
         <v>119991.4</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" t="n">
         <v>66691.39999999999</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" t="n">
         <v>53300</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" t="n">
         <v>20583.2</v>
       </c>
       <c r="K2" t="b">
@@ -2599,28 +1774,28 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" t="n">
         <v>79.8</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="n">
         <v>1.6</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" t="n">
         <v>78.2</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>33.2</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" t="n">
         <v>210.2</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" t="n">
         <v>8.1</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" t="n">
         <v>202.1</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" t="n">
         <v>73</v>
       </c>
       <c r="K3" t="b">
@@ -2638,28 +1813,28 @@
           <t>Tianjin</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" t="n">
         <v>303.7</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="n">
         <v>122.8</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" t="n">
         <v>180.9</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>30.1</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" t="n">
         <v>1027.9</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" t="n">
         <v>474</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" t="n">
         <v>553.8</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" t="n">
         <v>75.3</v>
       </c>
       <c r="K4" t="b">
@@ -2677,28 +1852,28 @@
           <t>Hebei</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" t="n">
         <v>1338.8</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="n">
         <v>657.9</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" t="n">
         <v>680.9</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>284.4</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" t="n">
         <v>8462.9</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" t="n">
         <v>4873.2</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" t="n">
         <v>3589.7</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" t="n">
         <v>2336</v>
       </c>
       <c r="K5" t="b">
@@ -2716,28 +1891,28 @@
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" t="n">
         <v>1473.3</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="n">
         <v>935.1</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" t="n">
         <v>538.2</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>196.5</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" t="n">
         <v>4950.5</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" t="n">
         <v>3436.4</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" t="n">
         <v>1514.1</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" t="n">
         <v>776.7</v>
       </c>
       <c r="K6" t="b">
@@ -2755,28 +1930,28 @@
           <t>Inner Mongolia</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" t="n">
         <v>1244.6</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>1054.4</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>190.2</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>54.3</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" t="n">
         <v>6055.5</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" t="n">
         <v>5563.9</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" t="n">
         <v>491.6</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" t="n">
         <v>185</v>
       </c>
       <c r="K7" t="b">
@@ -2794,28 +1969,28 @@
           <t>Liaoning</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" t="n">
         <v>340.7</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="n">
         <v>67</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" t="n">
         <v>273.7</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>141.2</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" t="n">
         <v>1554.6</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" t="n">
         <v>609.1</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" t="n">
         <v>945.6</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" t="n">
         <v>683.4</v>
       </c>
       <c r="K8" t="b">
@@ -2833,28 +2008,28 @@
           <t>Jilin</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" t="n">
         <v>141.5</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" t="n">
         <v>56.3</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" t="n">
         <v>85.2</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>61</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" t="n">
         <v>724.5</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" t="n">
         <v>438.3</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" t="n">
         <v>286.2</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" t="n">
         <v>168.4</v>
       </c>
       <c r="K9" t="b">
@@ -2872,28 +2047,28 @@
           <t>Heilongjiang</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" t="n">
         <v>200.1</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" t="n">
         <v>67.5</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" t="n">
         <v>132.6</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" t="n">
         <v>917.1</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" t="n">
         <v>537.8</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" t="n">
         <v>379.3</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" t="n">
         <v>154.7</v>
       </c>
       <c r="K10" t="b">
@@ -2911,28 +2086,28 @@
           <t>Shanghai</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" t="n">
         <v>213.7</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" t="n">
         <v>22.2</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" t="n">
         <v>191.5</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" t="n">
         <v>27.4</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" t="n">
         <v>625.1</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" t="n">
         <v>62</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" t="n">
         <v>563.2</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" t="n">
         <v>50.2</v>
       </c>
       <c r="K11" t="b">
@@ -2950,28 +2125,28 @@
           <t>Jiangsu</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" t="n">
         <v>2803.9</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" t="n">
         <v>972.3</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" t="n">
         <v>1831.6</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" t="n">
         <v>513.9</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" t="n">
         <v>8968.4</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" t="n">
         <v>2567.1</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" t="n">
         <v>6401.3</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" t="n">
         <v>2228</v>
       </c>
       <c r="K12" t="b">
@@ -2989,28 +2164,28 @@
           <t>Zhejiang</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" t="n">
         <v>1701.9</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" t="n">
         <v>311.4</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" t="n">
         <v>1390.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" t="n">
         <v>160.7</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" t="n">
         <v>6429.4</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" t="n">
         <v>1145.3</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" t="n">
         <v>5284.1</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" t="n">
         <v>612.8</v>
       </c>
       <c r="K13" t="b">
@@ -3028,28 +2203,28 @@
           <t>Anhui</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" t="n">
         <v>1314.2</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" t="n">
         <v>217.7</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" t="n">
         <v>1096.5</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" t="n">
         <v>313.9</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" t="n">
         <v>5625.5</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" t="n">
         <v>1659.6</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" t="n">
         <v>3965.8</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" t="n">
         <v>1812.9</v>
       </c>
       <c r="K14" t="b">
@@ -3067,28 +2242,28 @@
           <t>Fujian</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" t="n">
         <v>476.7</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" t="n">
         <v>61.3</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" t="n">
         <v>415.4</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" t="n">
         <v>107.1</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" t="n">
         <v>1734.4</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" t="n">
         <v>137.2</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" t="n">
         <v>1597.2</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" t="n">
         <v>616.6</v>
       </c>
       <c r="K15" t="b">
@@ -3106,28 +2281,28 @@
           <t>Jiangxi</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" t="n">
         <v>303.4</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>21.9</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>281.5</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" t="n">
         <v>109.9</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="n">
         <v>2872.3</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" t="n">
         <v>1400.2</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" t="n">
         <v>1472.1</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" t="n">
         <v>784.3</v>
       </c>
       <c r="K16" t="b">
@@ -3145,28 +2320,28 @@
           <t>Shandong</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" t="n">
         <v>1871.4</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>823.1</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>1048.3</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" t="n">
         <v>179.8</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" t="n">
         <v>9484.9</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" t="n">
         <v>3416</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" t="n">
         <v>6068.9</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" t="n">
         <v>2940.3</v>
       </c>
       <c r="K17" t="b">
@@ -3184,28 +2359,28 @@
           <t>Henan</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" t="n">
         <v>1216.7</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" t="n">
         <v>47.5</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" t="n">
         <v>1169.2</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" t="n">
         <v>591.5</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" t="n">
         <v>5565.8</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" t="n">
         <v>677.5</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" t="n">
         <v>4888.3</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" t="n">
         <v>2897.7</v>
       </c>
       <c r="K18" t="b">
@@ -3223,28 +2398,28 @@
           <t>Hubei</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" t="n">
         <v>974.6</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" t="n">
         <v>894.2</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" t="n">
         <v>177.3</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" t="n">
         <v>4484.5</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" t="n">
         <v>2228.2</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" t="n">
         <v>2256.3</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" t="n">
         <v>496.7</v>
       </c>
       <c r="K19" t="b">
@@ -3262,28 +2437,28 @@
           <t>Hunan</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" t="n">
         <v>901</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" t="n">
         <v>258</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" t="n">
         <v>643</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" t="n">
         <v>299.6</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" t="n">
         <v>2743.9</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" t="n">
         <v>713.5</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" t="n">
         <v>2030.4</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" t="n">
         <v>1200.6</v>
       </c>
       <c r="K20" t="b">
@@ -3301,28 +2476,28 @@
           <t>Guangdong</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" t="n">
         <v>2132.5</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" t="n">
         <v>508.8</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" t="n">
         <v>1623.7</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" t="n">
         <v>471.5</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" t="n">
         <v>6248</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" t="n">
         <v>1608.9</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" t="n">
         <v>4639.1</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" t="n">
         <v>850.1</v>
       </c>
       <c r="K21" t="b">
@@ -3340,28 +2515,28 @@
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" t="n">
         <v>1145</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" t="n">
         <v>472.5</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" t="n">
         <v>672.5</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" t="n">
         <v>27.5</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" t="n">
         <v>3273.8</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" t="n">
         <v>1391.2</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" t="n">
         <v>1882.6</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="K22" t="b">
@@ -3379,28 +2554,28 @@
           <t>Hainan</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" t="n">
         <v>219.3</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" t="n">
         <v>127</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" t="n">
         <v>92.2</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" t="n">
         <v>9.5</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" t="n">
         <v>960.1</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" t="n">
         <v>598.3</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" t="n">
         <v>361.7</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" t="n">
         <v>34</v>
       </c>
       <c r="K23" t="b">
@@ -3418,28 +2593,28 @@
           <t>Chongqing</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" t="n">
         <v>275.3</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" t="n">
         <v>51.4</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" t="n">
         <v>223.9</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" t="n">
         <v>45.4</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" t="n">
         <v>585</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" t="n">
         <v>154.9</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" t="n">
         <v>430.1</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" t="n">
         <v>51.7</v>
       </c>
       <c r="K24" t="b">
@@ -3457,28 +2632,28 @@
           <t>Sichuan</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" t="n">
         <v>897.8</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" t="n">
         <v>432.6</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" t="n">
         <v>465.1</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" t="n">
         <v>151.2</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" t="n">
         <v>1980.1</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" t="n">
         <v>1321.9</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" t="n">
         <v>658.2</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" t="n">
         <v>175.1</v>
       </c>
       <c r="K25" t="b">
@@ -3496,28 +2671,28 @@
           <t>Guizhou</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" t="n">
         <v>886.3</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" t="n">
         <v>697.7</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" t="n">
         <v>188.5</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" t="n">
         <v>130.7</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" t="n">
         <v>2871.9</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" t="n">
         <v>2573.9</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" t="n">
         <v>298</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" t="n">
         <v>183</v>
       </c>
       <c r="K26" t="b">
@@ -3535,28 +2710,28 @@
           <t>Yunnan</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" t="n">
         <v>1762.9</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" t="n">
         <v>1531.4</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" t="n">
         <v>231.5</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" t="n">
         <v>155.1</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" t="n">
         <v>5486.1</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" t="n">
         <v>4964.6</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" t="n">
         <v>521.4</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" t="n">
         <v>363.8</v>
       </c>
       <c r="K27" t="b">
@@ -3574,28 +2749,28 @@
           <t>Tibet</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" t="n">
         <v>376.5</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" t="n">
         <v>375.9</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" t="n">
         <v>0.6</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
         <v>574.5</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" t="n">
         <v>568.5</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="b">
@@ -3613,28 +2788,28 @@
           <t>Shaanxi</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" t="n">
         <v>759.9</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" t="n">
         <v>293.2</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>466.7</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" t="n">
         <v>207.2</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" t="n">
         <v>4193</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" t="n">
         <v>2817.3</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" t="n">
         <v>1375.8</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" t="n">
         <v>640.2</v>
       </c>
       <c r="K29" t="b">
@@ -3652,28 +2827,28 @@
           <t>Gansu</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" t="n">
         <v>714.2</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" t="n">
         <v>613.8</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" t="n">
         <v>100.3</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" t="n">
         <v>24.4</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" t="n">
         <v>3853</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" t="n">
         <v>3568.7</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" t="n">
         <v>284.3</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="K30" t="b">
@@ -3691,28 +2866,28 @@
           <t>Qinghai</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" t="n">
         <v>615.5</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>604.9</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>10.6</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" t="n">
         <v>1.9</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" t="n">
         <v>4257.6</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" t="n">
         <v>4209.2</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" t="n">
         <v>48.4</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" t="n">
         <v>7.3</v>
       </c>
       <c r="K31" t="b">
@@ -3730,28 +2905,28 @@
           <t>Ningxia</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" t="n">
         <v>1556.9</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" t="n">
         <v>1467.2</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" t="n">
         <v>89.7</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" t="n">
         <v>21.6</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" t="n">
         <v>4180.9</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" t="n">
         <v>3916.4</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" t="n">
         <v>264.5</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" t="n">
         <v>38.6</v>
       </c>
       <c r="K32" t="b">
@@ -3769,28 +2944,28 @@
           <t>Xinjiang</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" t="n">
         <v>3415.4</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>3402.1</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>13.3</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" t="n">
         <v>1.7</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" t="n">
         <v>9090.1</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" t="n">
         <v>9050.1</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" t="n">
         <v>40.1</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" t="n">
         <v>8</v>
       </c>
       <c r="K33" t="b">
@@ -3810,129 +2985,116 @@
   </sheetPr>
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="31" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>province_cn</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>province_en</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_total_10kw</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_utility_10kw</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_distributed_10kw</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>new_capacity_residential_10kw</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_total_10kw</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_utility_10kw</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_distributed_10kw</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cum_capacity_residential_10kw</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>province_translation_missing</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Province (raw OCR CN)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Province (EN translation)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>New capacity total</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>New utility-scale</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>New distributed</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>New residential</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Cumulative total</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Cumulative utility-scale</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Cumulative distributed</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Cumulative residential</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Translation missing?</t>
         </is>
@@ -4006,28 +3168,28 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" t="n">
         <v>31657.4</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="n">
         <v>16357</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" t="n">
         <v>15300.3</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>4594.7</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" t="n">
         <v>119991.4</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" t="n">
         <v>66691.39999999999</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" t="n">
         <v>53300</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" t="n">
         <v>20583.2</v>
       </c>
       <c r="K4" t="b">
@@ -4045,28 +3207,28 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" t="n">
         <v>79.8</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="n">
         <v>1.6</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" t="n">
         <v>78.2</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>33.2</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" t="n">
         <v>210.2</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" t="n">
         <v>8.1</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" t="n">
         <v>202.1</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" t="n">
         <v>73</v>
       </c>
       <c r="K5" t="b">
@@ -4084,28 +3246,28 @@
           <t>Tianjin</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" t="n">
         <v>303.7</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="n">
         <v>122.8</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" t="n">
         <v>180.9</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>30.1</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" t="n">
         <v>1027.9</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" t="n">
         <v>474</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" t="n">
         <v>553.8</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" t="n">
         <v>75.3</v>
       </c>
       <c r="K6" t="b">
@@ -4123,28 +3285,28 @@
           <t>Hebei</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" t="n">
         <v>1338.8</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>657.9</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>680.9</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>284.4</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" t="n">
         <v>8462.9</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" t="n">
         <v>4873.2</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" t="n">
         <v>3589.7</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" t="n">
         <v>2336</v>
       </c>
       <c r="K7" t="b">
@@ -4162,28 +3324,28 @@
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" t="n">
         <v>1473.3</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="n">
         <v>935.1</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" t="n">
         <v>538.2</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>196.5</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" t="n">
         <v>4950.5</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" t="n">
         <v>3436.4</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" t="n">
         <v>1514.1</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" t="n">
         <v>776.7</v>
       </c>
       <c r="K8" t="b">
@@ -4201,28 +3363,28 @@
           <t>Inner Mongolia</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" t="n">
         <v>1244.6</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" t="n">
         <v>1054.4</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" t="n">
         <v>190.2</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>54.3</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" t="n">
         <v>6055.5</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" t="n">
         <v>5563.9</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" t="n">
         <v>491.6</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" t="n">
         <v>185</v>
       </c>
       <c r="K9" t="b">
@@ -4240,28 +3402,28 @@
           <t>Liaoning</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" t="n">
         <v>340.7</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" t="n">
         <v>67</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" t="n">
         <v>273.7</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" t="n">
         <v>141.2</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" t="n">
         <v>1554.6</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" t="n">
         <v>609.1</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" t="n">
         <v>945.6</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" t="n">
         <v>683.4</v>
       </c>
       <c r="K10" t="b">
@@ -4279,28 +3441,28 @@
           <t>Jilin</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" t="n">
         <v>141.5</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" t="n">
         <v>56.3</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" t="n">
         <v>85.2</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" t="n">
         <v>61</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" t="n">
         <v>724.5</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" t="n">
         <v>438.3</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" t="n">
         <v>286.2</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" t="n">
         <v>168.4</v>
       </c>
       <c r="K11" t="b">
@@ -4318,28 +3480,28 @@
           <t>Heilongjiang</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" t="n">
         <v>200.1</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" t="n">
         <v>67.5</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" t="n">
         <v>132.6</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" t="n">
         <v>917.1</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" t="n">
         <v>537.8</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" t="n">
         <v>379.3</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" t="n">
         <v>154.7</v>
       </c>
       <c r="K12" t="b">
@@ -4357,28 +3519,28 @@
           <t>Shanghai</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" t="n">
         <v>213.7</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" t="n">
         <v>22.2</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" t="n">
         <v>191.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" t="n">
         <v>27.4</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" t="n">
         <v>625.1</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" t="n">
         <v>62</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" t="n">
         <v>563.2</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" t="n">
         <v>50.2</v>
       </c>
       <c r="K13" t="b">
@@ -4396,28 +3558,28 @@
           <t>Jiangsu</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" t="n">
         <v>2803.9</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" t="n">
         <v>972.3</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" t="n">
         <v>1831.6</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" t="n">
         <v>513.9</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" t="n">
         <v>8968.4</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" t="n">
         <v>2567.1</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" t="n">
         <v>6401.3</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" t="n">
         <v>2228</v>
       </c>
       <c r="K14" t="b">
@@ -4435,28 +3597,28 @@
           <t>Zhejiang</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" t="n">
         <v>1701.9</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" t="n">
         <v>311.4</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" t="n">
         <v>1390.5</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" t="n">
         <v>160.7</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" t="n">
         <v>6429.4</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" t="n">
         <v>1145.3</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" t="n">
         <v>5284.1</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" t="n">
         <v>612.8</v>
       </c>
       <c r="K15" t="b">
@@ -4474,28 +3636,28 @@
           <t>Anhui</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" t="n">
         <v>1314.2</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>217.7</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>1096.5</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" t="n">
         <v>313.9</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="n">
         <v>5625.5</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" t="n">
         <v>1659.6</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" t="n">
         <v>3965.8</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" t="n">
         <v>1812.9</v>
       </c>
       <c r="K16" t="b">
@@ -4513,28 +3675,28 @@
           <t>Fujian</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" t="n">
         <v>476.7</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>61.3</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>415.4</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" t="n">
         <v>107.1</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" t="n">
         <v>1734.4</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" t="n">
         <v>137.2</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" t="n">
         <v>1597.2</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" t="n">
         <v>616.6</v>
       </c>
       <c r="K17" t="b">
@@ -4552,28 +3714,28 @@
           <t>Jiangxi</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" t="n">
         <v>303.4</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" t="n">
         <v>21.9</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" t="n">
         <v>281.5</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" t="n">
         <v>109.9</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" t="n">
         <v>2872.3</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" t="n">
         <v>1400.2</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" t="n">
         <v>1472.1</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" t="n">
         <v>784.3</v>
       </c>
       <c r="K18" t="b">
@@ -4591,28 +3753,28 @@
           <t>Shandong</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" t="n">
         <v>1871.4</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" t="n">
         <v>823.1</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" t="n">
         <v>1048.3</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" t="n">
         <v>179.8</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" t="n">
         <v>9484.9</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" t="n">
         <v>3416</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" t="n">
         <v>6068.9</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" t="n">
         <v>2940.3</v>
       </c>
       <c r="K19" t="b">
@@ -4630,28 +3792,28 @@
           <t>Henan</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" t="n">
         <v>1216.7</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" t="n">
         <v>47.5</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" t="n">
         <v>1169.2</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" t="n">
         <v>591.5</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" t="n">
         <v>5565.8</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" t="n">
         <v>677.5</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" t="n">
         <v>4888.3</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" t="n">
         <v>2897.7</v>
       </c>
       <c r="K20" t="b">
@@ -4669,28 +3831,28 @@
           <t>Hubei</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" t="n">
         <v>974.6</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" t="n">
         <v>894.2</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" t="n">
         <v>177.3</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" t="n">
         <v>4484.5</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" t="n">
         <v>2228.2</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" t="n">
         <v>2256.3</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" t="n">
         <v>496.7</v>
       </c>
       <c r="K21" t="b">
@@ -4708,28 +3870,28 @@
           <t>Hunan</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" t="n">
         <v>901</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" t="n">
         <v>258</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" t="n">
         <v>643</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" t="n">
         <v>299.6</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" t="n">
         <v>2743.9</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" t="n">
         <v>713.5</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" t="n">
         <v>2030.4</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" t="n">
         <v>1200.6</v>
       </c>
       <c r="K22" t="b">
@@ -4747,28 +3909,28 @@
           <t>Guangdong</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" t="n">
         <v>2132.5</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" t="n">
         <v>508.8</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" t="n">
         <v>1623.7</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" t="n">
         <v>471.5</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" t="n">
         <v>6248</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" t="n">
         <v>1608.9</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" t="n">
         <v>4639.1</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" t="n">
         <v>850.1</v>
       </c>
       <c r="K23" t="b">
@@ -4786,28 +3948,28 @@
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" t="n">
         <v>1145</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" t="n">
         <v>472.5</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" t="n">
         <v>672.5</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" t="n">
         <v>27.5</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" t="n">
         <v>3273.8</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" t="n">
         <v>1391.2</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" t="n">
         <v>1882.6</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="K24" t="b">
@@ -4825,28 +3987,28 @@
           <t>Hainan</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" t="n">
         <v>219.3</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" t="n">
         <v>127</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" t="n">
         <v>92.2</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" t="n">
         <v>9.5</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" t="n">
         <v>960.1</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" t="n">
         <v>598.3</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" t="n">
         <v>361.7</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" t="n">
         <v>34</v>
       </c>
       <c r="K25" t="b">
@@ -4864,28 +4026,28 @@
           <t>Chongqing</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" t="n">
         <v>275.3</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" t="n">
         <v>51.4</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" t="n">
         <v>223.9</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" t="n">
         <v>45.4</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" t="n">
         <v>585</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" t="n">
         <v>154.9</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" t="n">
         <v>430.1</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" t="n">
         <v>51.7</v>
       </c>
       <c r="K26" t="b">
@@ -4903,28 +4065,28 @@
           <t>Sichuan</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" t="n">
         <v>897.8</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" t="n">
         <v>432.6</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" t="n">
         <v>465.1</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" t="n">
         <v>151.2</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" t="n">
         <v>1980.1</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" t="n">
         <v>1321.9</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" t="n">
         <v>658.2</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" t="n">
         <v>175.1</v>
       </c>
       <c r="K27" t="b">
@@ -4942,28 +4104,28 @@
           <t>Guizhou</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" t="n">
         <v>886.3</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" t="n">
         <v>697.7</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" t="n">
         <v>188.5</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" t="n">
         <v>130.7</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" t="n">
         <v>2871.9</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" t="n">
         <v>2573.9</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" t="n">
         <v>298</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" t="n">
         <v>183</v>
       </c>
       <c r="K28" t="b">
@@ -4981,28 +4143,28 @@
           <t>Yunnan</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" t="n">
         <v>1762.9</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" t="n">
         <v>1531.4</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>231.5</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" t="n">
         <v>155.1</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" t="n">
         <v>5486.1</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" t="n">
         <v>4964.6</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" t="n">
         <v>521.4</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" t="n">
         <v>363.8</v>
       </c>
       <c r="K29" t="b">
@@ -5020,28 +4182,28 @@
           <t>Tibet</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" t="n">
         <v>376.5</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" t="n">
         <v>375.9</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" t="n">
         <v>0.6</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="n">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>574.5</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" t="n">
         <v>568.5</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="b">
@@ -5059,28 +4221,28 @@
           <t>Shaanxi</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" t="n">
         <v>759.9</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>293.2</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>466.7</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" t="n">
         <v>207.2</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" t="n">
         <v>4193</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" t="n">
         <v>2817.3</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" t="n">
         <v>1375.8</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" t="n">
         <v>640.2</v>
       </c>
       <c r="K31" t="b">
@@ -5098,28 +4260,28 @@
           <t>Gansu</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" t="n">
         <v>714.2</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" t="n">
         <v>613.8</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" t="n">
         <v>100.3</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" t="n">
         <v>24.4</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" t="n">
         <v>3853</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" t="n">
         <v>3568.7</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" t="n">
         <v>284.3</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="K32" t="b">
@@ -5137,28 +4299,28 @@
           <t>Qinghai</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" t="n">
         <v>615.5</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>604.9</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>10.6</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" t="n">
         <v>1.9</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" t="n">
         <v>4257.6</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" t="n">
         <v>4209.2</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" t="n">
         <v>48.4</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" t="n">
         <v>7.3</v>
       </c>
       <c r="K33" t="b">
@@ -5176,28 +4338,28 @@
           <t>Ningxia</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" t="n">
         <v>1556.9</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" t="n">
         <v>1467.2</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" t="n">
         <v>89.7</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" t="n">
         <v>21.6</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" t="n">
         <v>4180.9</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" t="n">
         <v>3916.4</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" t="n">
         <v>264.5</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J34" t="n">
         <v>38.6</v>
       </c>
       <c r="K34" t="b">
@@ -5215,28 +4377,28 @@
           <t>Xinjiang</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" t="n">
         <v>3415.4</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" t="n">
         <v>3402.1</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" t="n">
         <v>13.3</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" t="n">
         <v>1.7</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" t="n">
         <v>9090.1</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" t="n">
         <v>9050.1</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" t="n">
         <v>40.1</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" t="n">
         <v>8</v>
       </c>
       <c r="K35" t="b">
